--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.16.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.16.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -803,7 +803,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.16.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.16.xlsx
@@ -422,17 +422,17 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="27" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="39" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
@@ -599,22 +599,30 @@
         </is>
       </c>
       <c r="I2" s="1" t="inlineStr"/>
-      <c r="J2" s="1" t="inlineStr"/>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>L8: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON | isolated marker/symbol line :: 1 ；</t>
+        </is>
+      </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L93: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]9</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]9</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>L9: isolated marker/symbol line :: ;</t>
+          <t>L8: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON | isolated marker/symbol line :: 1 ；</t>
         </is>
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L61: isolated marker/symbol line :: 1;</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]9</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -645,7 +653,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>74</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -655,17 +663,21 @@
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr"/>
-      <c r="K3" s="1" t="inlineStr"/>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>L93: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L10: isolated marker/symbol line :: 4</t>
+          <t>L9: isolated marker/symbol line :: ;</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L93: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L61: isolated marker/symbol line :: 1;</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -707,10 +719,14 @@
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L39: isolated marker/symbol line :: 9</t>
-        </is>
-      </c>
-      <c r="O4" s="1" t="inlineStr"/>
+          <t>L10: isolated marker/symbol line :: 4</t>
+        </is>
+      </c>
+      <c r="O4" s="1" t="inlineStr">
+        <is>
+          <t>L93: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr"/>
       <c r="R4" s="1" t="inlineStr"/>
@@ -730,12 +746,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -748,7 +764,11 @@
       <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
-      <c r="N5" s="1" t="inlineStr"/>
+      <c r="N5" s="1" t="inlineStr">
+        <is>
+          <t>L39: isolated marker/symbol line :: 9</t>
+        </is>
+      </c>
       <c r="O5" s="1" t="inlineStr"/>
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr"/>
@@ -925,12 +945,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -969,7 +989,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1003,12 +1023,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
